--- a/60000-80000.xlsx
+++ b/60000-80000.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="91">
   <si>
     <t>CVR</t>
   </si>
@@ -154,6 +154,15 @@
     <t>10658446</t>
   </si>
   <si>
+    <t>27485111</t>
+  </si>
+  <si>
+    <t>34230625</t>
+  </si>
+  <si>
+    <t>15603712</t>
+  </si>
+  <si>
     <t>Visma Expense</t>
   </si>
   <si>
@@ -190,6 +199,9 @@
     <t>BPO Visma Løn</t>
   </si>
   <si>
+    <t>Time</t>
+  </si>
+  <si>
     <t>Anden årsag (angiv hvilken i bemærkninger)</t>
   </si>
   <si>
@@ -269,6 +281,9 @@
   </si>
   <si>
     <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
   </si>
   <si>
     <t>60000-80000</t>
@@ -633,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -676,19 +691,19 @@
         <v>78556.39999999999</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2">
         <v>44200</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -702,22 +717,22 @@
         <v>77346.97</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2">
         <v>44208</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -731,19 +746,19 @@
         <v>72038.67999999999</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2">
         <v>44314</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -757,19 +772,19 @@
         <v>74992</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2">
         <v>44347</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -783,19 +798,19 @@
         <v>79410</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2">
         <v>44355</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -809,22 +824,22 @@
         <v>78696</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2">
         <v>44371</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -838,19 +853,19 @@
         <v>72578.35000000001</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2">
         <v>44463</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -864,19 +879,19 @@
         <v>72674.92</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2">
         <v>44469</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -890,22 +905,22 @@
         <v>61133.08</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2">
         <v>44498</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -919,22 +934,22 @@
         <v>74156.7</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2">
         <v>44509</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -948,19 +963,19 @@
         <v>77675.48</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2">
         <v>44498</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -974,19 +989,19 @@
         <v>65365</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2">
         <v>44530</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1000,19 +1015,19 @@
         <v>65843.74000000001</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2">
         <v>44592</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1026,19 +1041,19 @@
         <v>78090</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2">
         <v>44602</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1052,19 +1067,19 @@
         <v>79981.99000000001</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2">
         <v>44617</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1078,19 +1093,19 @@
         <v>73747</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2">
         <v>44617</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1104,19 +1119,19 @@
         <v>61008</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2">
         <v>44811</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1130,19 +1145,19 @@
         <v>61182</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2">
         <v>44858</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1156,19 +1171,19 @@
         <v>75638</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2">
         <v>44858</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1197,19 @@
         <v>71046</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2">
         <v>44865</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,16 +1223,16 @@
         <v>74171</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2">
         <v>45015</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1231,16 +1246,16 @@
         <v>71414.8</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2">
         <v>45029</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1254,16 +1269,16 @@
         <v>71077.63</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2">
         <v>45047</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1277,16 +1292,16 @@
         <v>76044</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2">
         <v>45072</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1300,16 +1315,16 @@
         <v>74972.74000000001</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2">
         <v>45104</v>
       </c>
       <c r="H26" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1323,16 +1338,16 @@
         <v>70780</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2">
         <v>45145</v>
       </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1346,19 +1361,19 @@
         <v>75401.86</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2">
         <v>45167</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1372,16 +1387,16 @@
         <v>69120</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E29" s="2">
         <v>45044</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1395,16 +1410,16 @@
         <v>60860</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2">
         <v>45168</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1418,16 +1433,16 @@
         <v>65688</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2">
         <v>45211</v>
       </c>
       <c r="H31" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1441,16 +1456,16 @@
         <v>76625</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2">
         <v>45301</v>
       </c>
       <c r="H32" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1464,16 +1479,16 @@
         <v>74419</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2">
         <v>45306</v>
       </c>
       <c r="H33" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1487,16 +1502,16 @@
         <v>66672</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E34" s="2">
         <v>45407</v>
       </c>
       <c r="H34" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1510,19 +1525,19 @@
         <v>78804</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2">
         <v>45469</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I35" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1536,16 +1551,16 @@
         <v>60060</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2">
         <v>45498</v>
       </c>
       <c r="H36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1559,16 +1574,16 @@
         <v>67236</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2">
         <v>45513</v>
       </c>
       <c r="H37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1582,16 +1597,16 @@
         <v>69000</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2">
         <v>45551</v>
       </c>
       <c r="H38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1605,16 +1620,88 @@
         <v>61860</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2">
         <v>45561</v>
       </c>
       <c r="H39" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>2024</v>
+      </c>
+      <c r="C40">
+        <v>63448.08</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45574</v>
+      </c>
+      <c r="G40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
+        <v>2024</v>
+      </c>
+      <c r="C41">
+        <v>76470</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45565</v>
+      </c>
+      <c r="H41" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
+        <v>2024</v>
+      </c>
+      <c r="C42">
+        <v>75936</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45579</v>
+      </c>
+      <c r="H42" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
